--- a/uploads/archive/MKU 17.xlsx
+++ b/uploads/archive/MKU 17.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\file rendy\DATA KIRIMAN\MKU\2026\9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\file rendy\DATA KIRIMAN\MKU\2026\10\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$L$83</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="257">
   <si>
     <t>No. Urut</t>
   </si>
@@ -60,709 +60,730 @@
     <t>Qty BS</t>
   </si>
   <si>
-    <t>SO-KU/2609/160005</t>
+    <t>SO-KU/2610/160001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Seminyak </t>
+  </si>
+  <si>
+    <t>FROZEN</t>
+  </si>
+  <si>
+    <t>NAUGHTY NURIS SEMINYAK</t>
+  </si>
+  <si>
+    <t>NN Sujana</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PSJ0027</t>
+  </si>
+  <si>
+    <t>Iga Babi Super</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160002</t>
+  </si>
+  <si>
+    <t>Denpasar  - Utara</t>
+  </si>
+  <si>
+    <t>DRY</t>
+  </si>
+  <si>
+    <t>MB FROZEN FOOD</t>
+  </si>
+  <si>
+    <t>Ni Ketut Sriasih (GT)</t>
+  </si>
+  <si>
+    <t>POT0161</t>
+  </si>
+  <si>
+    <t>La Valle Whole Peeled Tomatoes 2.5 Kg</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160003</t>
+  </si>
+  <si>
+    <t>PSJ0019</t>
+  </si>
+  <si>
+    <t>Pork B Sliced (1kg/pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Kuta </t>
+  </si>
+  <si>
+    <t>SHINTA WARUNG</t>
+  </si>
+  <si>
+    <t>Wahyu</t>
+  </si>
+  <si>
+    <t>POS0025</t>
+  </si>
+  <si>
+    <t>O Sole Doppio Concentrato Paste Tomato 2.2 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denpasar  - Selatan </t>
+  </si>
+  <si>
+    <t>AGUNA COFFEE</t>
+  </si>
+  <si>
+    <t>I MADE LUIH</t>
+  </si>
+  <si>
+    <t>PMS0059</t>
+  </si>
+  <si>
+    <t>Flavour Artisan - Belgian Signature Dark Chocolate (80 Cocoa%)  500gr</t>
+  </si>
+  <si>
+    <t>PACK</t>
+  </si>
+  <si>
+    <t>PMS0114</t>
+  </si>
+  <si>
+    <t>Masterista Cold Foam Sea Salt 500 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160008</t>
+  </si>
+  <si>
+    <t>BADUNG  - Jimbaran Uluwatu</t>
+  </si>
+  <si>
+    <t>CENDOL RATU</t>
+  </si>
+  <si>
+    <t>Juni</t>
+  </si>
+  <si>
+    <t>PMS0076</t>
+  </si>
+  <si>
+    <t>Masterista Creamer Base (Creamy)</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160009</t>
+  </si>
+  <si>
+    <t>LITTLE ITALY</t>
+  </si>
+  <si>
+    <t>PDM0004</t>
+  </si>
+  <si>
+    <t>Armando Spaghetti 500 Gr/Pack</t>
+  </si>
+  <si>
+    <t>PIF0012</t>
+  </si>
+  <si>
+    <t>Pristine Classic Cooking Cream 1 Lt</t>
+  </si>
+  <si>
+    <t>LTR</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160010</t>
+  </si>
+  <si>
+    <t>WACKO PETITENGET</t>
+  </si>
+  <si>
+    <t>Sujana</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160011</t>
+  </si>
+  <si>
+    <t>LA BRASSERIE JIMBARAN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160012</t>
+  </si>
+  <si>
+    <t>ZERO 4 KARAOKE</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160013</t>
+  </si>
+  <si>
+    <t>LE CROISSANT</t>
+  </si>
+  <si>
+    <t>PMS0094</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Butterscotch 850 Ml</t>
+  </si>
+  <si>
+    <t>BTL</t>
+  </si>
+  <si>
+    <t>PMS0144</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Peach 850ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160014</t>
+  </si>
+  <si>
+    <t>KILO RESTAURANT</t>
+  </si>
+  <si>
+    <t>PMS0140</t>
+  </si>
+  <si>
+    <t>Masterista Japanese Matcha Powder Premium 500 Ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160015</t>
+  </si>
+  <si>
+    <t>ZIA TINA BALI</t>
+  </si>
+  <si>
+    <t>ASS-CH-L250</t>
+  </si>
+  <si>
+    <t>Chamomile Dream @250gr</t>
+  </si>
+  <si>
+    <t>ASS-JT-LP250</t>
+  </si>
+  <si>
+    <t>Jasmine Tea @250gr/Pouch</t>
+  </si>
+  <si>
+    <t>POU</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BADUNG  - Canggu </t>
+  </si>
+  <si>
+    <t>SAKURA BAR CANGGU</t>
+  </si>
+  <si>
+    <t>Taufik</t>
+  </si>
+  <si>
+    <t>CKP1S-159</t>
+  </si>
+  <si>
+    <t>Daebak Soju Lemon @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-160</t>
+  </si>
+  <si>
+    <t>Daebak Soju Mango @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-163</t>
+  </si>
+  <si>
+    <t>Daebak Soju Peach @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-164</t>
+  </si>
+  <si>
+    <t>Daebak Soju Lychee @360ml/btl</t>
+  </si>
+  <si>
+    <t>CKP1S-165</t>
+  </si>
+  <si>
+    <t>Daebak Soju Original 360ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160017</t>
   </si>
   <si>
     <t>BADUNG  - NusaDua</t>
   </si>
   <si>
-    <t>DRY</t>
-  </si>
-  <si>
-    <t>AYODYA RESORT BALI</t>
+    <t>PLATINUM HOTEL JIMBARAN BEACH BAR</t>
   </si>
   <si>
     <t>Monica</t>
   </si>
   <si>
-    <t>PMS0176</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Melon Cream 850 Ml</t>
-  </si>
-  <si>
-    <t>BTL</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Seminyak </t>
-  </si>
-  <si>
-    <t>JOHNNY ROCKET SEMINYAK</t>
-  </si>
-  <si>
-    <t>Sujana</t>
-  </si>
-  <si>
-    <t>PIF0011</t>
-  </si>
-  <si>
-    <t>Pristine Classic Whip Topping 1 Lt</t>
-  </si>
-  <si>
-    <t>LTR</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denpasar  - Selatan </t>
-  </si>
-  <si>
-    <t>JOHNNY ROCKET GRAND OUTLET BALI</t>
-  </si>
-  <si>
-    <t>Wahyu</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Kuta </t>
-  </si>
-  <si>
-    <t>JOHNNY ROCKET BANDARA INTERNASIONAL</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160009</t>
-  </si>
-  <si>
-    <t>Denpasar  - Sanur, Ketewel</t>
-  </si>
-  <si>
-    <t>JOHNNY ROCKET ICON BALI</t>
-  </si>
-  <si>
-    <t>I MADE LUIH</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160010</t>
-  </si>
-  <si>
-    <t>BALE UDANG MANG ENGKING</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>PMS0028</t>
-  </si>
-  <si>
-    <t>Masterista Taro Expecta 800Gr</t>
-  </si>
-  <si>
-    <t>POU</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160011</t>
-  </si>
-  <si>
-    <t>JOHNNY ROCKET (BEACHWALK)</t>
-  </si>
-  <si>
-    <t>PIF0012</t>
-  </si>
-  <si>
-    <t>Pristine Classic Cooking Cream 1 Lt</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160013</t>
-  </si>
-  <si>
-    <t>Gianyar  - Gianyar</t>
-  </si>
-  <si>
-    <t>KERAMAS AERO PARK</t>
+    <t>SO-KU/2610/160018</t>
+  </si>
+  <si>
+    <t>FEBRIS HOTEL</t>
+  </si>
+  <si>
+    <t>Ronald</t>
+  </si>
+  <si>
+    <t>PAA0001</t>
+  </si>
+  <si>
+    <t>Bergold Mozzarella Block</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denpasar  - Barat </t>
+  </si>
+  <si>
+    <t>PT. GELATO FACTORY BALI</t>
+  </si>
+  <si>
+    <t>PMS0036</t>
+  </si>
+  <si>
+    <t>Artisan Pure Matcha (500Gr/Pack)</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160021</t>
+  </si>
+  <si>
+    <t>Gianyar  - Ubud</t>
+  </si>
+  <si>
+    <t>METLAND VENYA UBUD</t>
   </si>
   <si>
     <t>Picrom Stalyon</t>
   </si>
   <si>
-    <t>SO-KU/2609/160014</t>
-  </si>
-  <si>
-    <t>FROZEN</t>
-  </si>
-  <si>
-    <t>NAUGHTY NURIS SEMINYAK</t>
-  </si>
-  <si>
-    <t>NN Sujana</t>
-  </si>
-  <si>
-    <t>PSJ0026</t>
-  </si>
-  <si>
-    <t>Samcan Babi Tanpa Kulit</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160015</t>
-  </si>
-  <si>
-    <t>CAPRI BALI</t>
-  </si>
-  <si>
-    <t>POS0024</t>
-  </si>
-  <si>
-    <t>O Sole Pomodori Pelati Peeled Tomatoes 2.5Kg</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160016</t>
+    <t>PAS0014</t>
+  </si>
+  <si>
+    <t>Crr Rock'n Hash Brown Triangular 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>KTN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160022</t>
+  </si>
+  <si>
+    <t>GROUND ZERO KITCHEN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160023</t>
+  </si>
+  <si>
+    <t>FINNS BEACH CLUB</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denpasar  - Timur </t>
+  </si>
+  <si>
+    <t>UD. ZIO PANGAN JAYA</t>
+  </si>
+  <si>
+    <t>Wira</t>
+  </si>
+  <si>
+    <t>PAA0004</t>
+  </si>
+  <si>
+    <t>Bergold Pikant Mozzarella Block</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160025</t>
+  </si>
+  <si>
+    <t>IAS FOOD SERVICES</t>
+  </si>
+  <si>
+    <t>PMS0024</t>
+  </si>
+  <si>
+    <t>Masterista Original Matcha 800Gr</t>
+  </si>
+  <si>
+    <t>PMS0026</t>
+  </si>
+  <si>
+    <t>Masterista Dark Chocolate 800Gr</t>
+  </si>
+  <si>
+    <t>PMS0027</t>
+  </si>
+  <si>
+    <t>Masterista Red Velvet Expecta 800Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160026</t>
+  </si>
+  <si>
+    <t>PT. GLOBAL BUANA PREMIUM</t>
+  </si>
+  <si>
+    <t>PMS0038</t>
+  </si>
+  <si>
+    <t>Flavorista Chocolate base (1000Gr/Pack)</t>
+  </si>
+  <si>
+    <t>PMS0132</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Vanilla Tradition 850ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160027</t>
+  </si>
+  <si>
+    <t>AVIARI BISTRO</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160028</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160030</t>
+  </si>
+  <si>
+    <t>POT0038</t>
+  </si>
+  <si>
+    <t>Premium Straight Cut 2Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160031</t>
+  </si>
+  <si>
+    <t>COFFEE CARTEL</t>
+  </si>
+  <si>
+    <t>PAS0036</t>
+  </si>
+  <si>
+    <t>Crr Rock'n Hash Brown Triangular 2.5Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160032</t>
+  </si>
+  <si>
+    <t>CENTRAL KITCHEN BALI</t>
+  </si>
+  <si>
+    <t>POT0120</t>
+  </si>
+  <si>
+    <t>Bottegaio Umbro Olio Evo Cucina 5Lt</t>
+  </si>
+  <si>
+    <t>GLN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160033</t>
+  </si>
+  <si>
+    <t>PENINSULA BEACH RESORT</t>
+  </si>
+  <si>
+    <t>PAS0015</t>
+  </si>
+  <si>
+    <t>Crr Rock'n Super Crispy Jakets Spicy Wedges 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160034</t>
+  </si>
+  <si>
+    <t>GLAMP NUSA BALI</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160035</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160036</t>
+  </si>
+  <si>
+    <t>ALJAZEERAH RESTAURANT</t>
+  </si>
+  <si>
+    <t>ASS-MM-LP250</t>
+  </si>
+  <si>
+    <t>Morrocan Mint @250gr/Pouch</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160038</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>CV ZAYCO BOGA  ALIFA</t>
+  </si>
+  <si>
+    <t>Management Bali</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160041</t>
+  </si>
+  <si>
+    <t>ALAM KUL KUL</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160042</t>
+  </si>
+  <si>
+    <t>MERCURE BALI LEGIAN</t>
+  </si>
+  <si>
+    <t>POT0156</t>
+  </si>
+  <si>
+    <t>Premium Hash Brown 2.5Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160044</t>
+  </si>
+  <si>
+    <t>THE KAYON RESORT</t>
+  </si>
+  <si>
+    <t>ASS-CH-TB50</t>
+  </si>
+  <si>
+    <t>Chamomile Dream @50Tb/Box</t>
+  </si>
+  <si>
+    <t>BOX</t>
+  </si>
+  <si>
+    <t>ASS-EBT</t>
+  </si>
+  <si>
+    <t>English Breakfast@50TB/Box</t>
+  </si>
+  <si>
+    <t>ASS-JVJ</t>
+  </si>
+  <si>
+    <t>Javanese Jasmine Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>ASS-PE-TB50</t>
+  </si>
+  <si>
+    <t>Peppermint Tea @50tb/Box</t>
+  </si>
+  <si>
+    <t>ASS-PGT</t>
+  </si>
+  <si>
+    <t>Pure Green Tea @50TB/Box</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160045</t>
+  </si>
+  <si>
+    <t>RUNWAY CAFE &amp; EATERY DPS</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160046</t>
+  </si>
+  <si>
+    <t>PT. SSP TAURUS GEMILANG INDONESIA</t>
+  </si>
+  <si>
+    <t>PEA0010</t>
+  </si>
+  <si>
+    <t>Gold Box Extra Butter MP341 1 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160047</t>
+  </si>
+  <si>
+    <t>ASS-EG-LP250</t>
+  </si>
+  <si>
+    <t>Earl Grey @250gr</t>
+  </si>
+  <si>
+    <t>ASS-PP-LP250</t>
+  </si>
+  <si>
+    <t>Peppermint @250gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160048</t>
+  </si>
+  <si>
+    <t>HILTON HOTEL</t>
+  </si>
+  <si>
+    <t>POT0110</t>
+  </si>
+  <si>
+    <t>Bergold Shredded Pizza Topping Mozzarella</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160049</t>
+  </si>
+  <si>
+    <t>BELLA ITALIAN GRAND MAS</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160050</t>
+  </si>
+  <si>
+    <t>KAFIN</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160051</t>
+  </si>
+  <si>
+    <t>FOOD GALLERIA</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160052</t>
   </si>
   <si>
     <t>KOJA KITCHEN AND COFFEE</t>
   </si>
   <si>
-    <t>150226</t>
-  </si>
-  <si>
-    <t>Belly Skinless Premium (2.5Kg/Pack)</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160017</t>
-  </si>
-  <si>
-    <t>THE ALLEYS</t>
-  </si>
-  <si>
-    <t>POT0038</t>
-  </si>
-  <si>
-    <t>Premium Straight Cut 2Kg</t>
-  </si>
-  <si>
-    <t>PACK</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BADUNG  - Canggu </t>
-  </si>
-  <si>
-    <t>FINNS BEACH CLUB</t>
-  </si>
-  <si>
-    <t>Taufik</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160019</t>
-  </si>
-  <si>
-    <t>Denpasar  - Utara</t>
-  </si>
-  <si>
-    <t>BALI CIAMIK SORO</t>
-  </si>
-  <si>
-    <t>Wira</t>
-  </si>
-  <si>
-    <t>CKP1S-164</t>
-  </si>
-  <si>
-    <t>Daebak Soju Lychee @360ml/btl</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160020</t>
-  </si>
-  <si>
-    <t>SOOGUD COFFEE</t>
-  </si>
-  <si>
-    <t>PMS0038</t>
-  </si>
-  <si>
-    <t>Flavorista Chocolate base (1000Gr/Pack)</t>
-  </si>
-  <si>
-    <t>PMS0050</t>
-  </si>
-  <si>
-    <t>Ice Shaken Mango Tea (1000Gr/Pack)</t>
-  </si>
-  <si>
-    <t>PMS0072</t>
-  </si>
-  <si>
-    <t>ICE SHAKEN PEACH TEA 1000 GR</t>
-  </si>
-  <si>
-    <t>PMS0119</t>
-  </si>
-  <si>
-    <t>Masterista Sweet Sauce Caramel 500 Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denpasar  - Barat </t>
-  </si>
-  <si>
-    <t>PT. ADIKARYA PANGAN FRESHINDO</t>
-  </si>
-  <si>
-    <t>Ni Ketut Sriasih (MT)</t>
-  </si>
-  <si>
-    <t>CKP1S-154</t>
-  </si>
-  <si>
-    <t>Jinro Chamisul Soju Plum 360ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160022</t>
-  </si>
-  <si>
-    <t>BADUNG  - Jimbaran Uluwatu</t>
-  </si>
-  <si>
-    <t>AUTOGRILL</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160023</t>
-  </si>
-  <si>
-    <t>BAMBU BALI ULUWATU</t>
-  </si>
-  <si>
-    <t>Juni</t>
-  </si>
-  <si>
-    <t>PAL0003</t>
-  </si>
-  <si>
-    <t>Isabi Smoked Salmon Slice 1Kg/Pack</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160024</t>
-  </si>
-  <si>
-    <t>PT. SSP TAURUS GEMILANG INDONESIA</t>
-  </si>
-  <si>
-    <t>PEA0010</t>
-  </si>
-  <si>
-    <t>Gold Box Extra Butter MP341 1 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160025</t>
-  </si>
-  <si>
-    <t>JALAPENO CANGGU</t>
+    <t>PQW0010</t>
+  </si>
+  <si>
+    <t>IQF FF Shoestring 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160053</t>
+  </si>
+  <si>
+    <t>WARUNG LOKAL</t>
   </si>
   <si>
     <t>Dewi Kristiani</t>
   </si>
   <si>
-    <t>PEA0007</t>
-  </si>
-  <si>
-    <t>Gold Box Melange Butter MP331 250 Gr - Sample</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160026</t>
-  </si>
-  <si>
-    <t>AMOLAS CAFE</t>
-  </si>
-  <si>
-    <t>ASS-CH-TB50</t>
-  </si>
-  <si>
-    <t>Chamomile Dream @50Tb/Box</t>
-  </si>
-  <si>
-    <t>BOX</t>
-  </si>
-  <si>
-    <t>ASS-EBT</t>
-  </si>
-  <si>
-    <t>English Breakfast@50TB/Box</t>
-  </si>
-  <si>
-    <t>ASS-EGT</t>
-  </si>
-  <si>
-    <t>Earl Grey @50TB/Box</t>
-  </si>
-  <si>
-    <t>ASS-PE-TB50</t>
-  </si>
-  <si>
-    <t>Peppermint Tea @50tb/Box</t>
-  </si>
-  <si>
-    <t>ASS-PGT</t>
-  </si>
-  <si>
-    <t>Pure Green Tea @50TB/Box</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160027</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160028</t>
-  </si>
-  <si>
-    <t>DISCOVERY KARTIKA PLAZA HOTEL</t>
-  </si>
-  <si>
-    <t>Ronald</t>
-  </si>
-  <si>
-    <t>PAA0002</t>
-  </si>
-  <si>
-    <t>Bergold Mozzarella Block 200 Gr</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160029</t>
-  </si>
-  <si>
-    <t>Tabanan - Kediri, Mengwi, Baturiti, Bedugul</t>
-  </si>
-  <si>
-    <t>NOEMA RESOERT PERERENAN</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160030</t>
-  </si>
-  <si>
-    <t>TRIBE HOTEL KUTA</t>
-  </si>
-  <si>
-    <t>PAA0001</t>
-  </si>
-  <si>
-    <t>Bergold Mozzarella Block</t>
-  </si>
-  <si>
-    <t>PQW0012</t>
-  </si>
-  <si>
-    <t>IQF FF Shoestring 2.5 Kg/Pack</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160031</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160032</t>
-  </si>
-  <si>
-    <t>MOVENPICK</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160033</t>
-  </si>
-  <si>
-    <t>BELLA ITALIAN GRAND MAS</t>
-  </si>
-  <si>
-    <t>PSJ0019</t>
-  </si>
-  <si>
-    <t>Pork B Sliced (1kg/pack)</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160034</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160035</t>
-  </si>
-  <si>
-    <t>Gianyar  - Ubud</t>
-  </si>
-  <si>
-    <t>SACRA STUJA UBUD</t>
-  </si>
-  <si>
-    <t>PMS0140</t>
-  </si>
-  <si>
-    <t>Masterista Japanese Matcha Powder Premium 500 Ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160036</t>
-  </si>
-  <si>
-    <t>PT. SOEJASCH BALI</t>
-  </si>
-  <si>
-    <t>Management Bali</t>
-  </si>
-  <si>
-    <t>POS0026</t>
-  </si>
-  <si>
-    <t>O Sole Olive Nere Denocciolate 4.1 Kg</t>
-  </si>
-  <si>
-    <t>POT0120</t>
-  </si>
-  <si>
-    <t>Bottegaio Umbro Olio Evo Cucina 5Lt</t>
-  </si>
-  <si>
-    <t>GLN</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160037</t>
-  </si>
-  <si>
-    <t>PEA0004</t>
-  </si>
-  <si>
-    <t>Gold Box Extra Butter MP341</t>
-  </si>
-  <si>
-    <t>POT0110</t>
-  </si>
-  <si>
-    <t>Bergold Shredded Pizza Topping Mozzarella</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160038</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160039</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160040</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160041</t>
-  </si>
-  <si>
-    <t>HILTON HOTEL</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160042</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160043</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160044</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160045</t>
-  </si>
-  <si>
-    <t>CHEEKY MONKEY</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160046</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160047</t>
+    <t>PAS0041</t>
+  </si>
+  <si>
+    <t>Maestro FF 10x10mm Straight Cut 2.5 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160054</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160061</t>
+  </si>
+  <si>
+    <t>MAMAS GERMAN REST.</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160062</t>
+  </si>
+  <si>
+    <t>PAS0026</t>
+  </si>
+  <si>
+    <t>Crr Rock'n Batter Skin On Fries 9x9mm 10Kg/Ctn</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160063</t>
+  </si>
+  <si>
+    <t>KOJA BAKERS &amp; INU COFFEE ROASTER</t>
+  </si>
+  <si>
+    <t>PMS0178</t>
+  </si>
+  <si>
+    <t>Masterista Ceremonial Pure Matcha Powder 500 Gr</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160064</t>
+  </si>
+  <si>
+    <t>WARUNG MADE SEMINYAK</t>
+  </si>
+  <si>
+    <t>CKPS014</t>
+  </si>
+  <si>
+    <t>Fashion Vodka Premium Quality</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160065</t>
+  </si>
+  <si>
+    <t>THREE COIN EATRY</t>
+  </si>
+  <si>
+    <t>PMS0131</t>
+  </si>
+  <si>
+    <t>Masterista Syrup Tropical Lychee 850 Ml</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160066</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160067</t>
+  </si>
+  <si>
+    <t>POTATO HEAD</t>
+  </si>
+  <si>
+    <t>PEA0003</t>
+  </si>
+  <si>
+    <t>Gold Box Melange Butter MP331</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160068</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160069</t>
+  </si>
+  <si>
+    <t>FRANKIES BAR AND GRILL</t>
+  </si>
+  <si>
+    <t>PEA0005</t>
+  </si>
+  <si>
+    <t>Gold Box Melange Butter MP331 5 Kg</t>
+  </si>
+  <si>
+    <t>SO-KU/2610/160070</t>
   </si>
   <si>
     <t>MAMAKA</t>
   </si>
   <si>
-    <t>SO-KU/2609/160048</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160049</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160050</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160051</t>
-  </si>
-  <si>
-    <t>KEDAI KOPI SIAP GIANYAR</t>
-  </si>
-  <si>
-    <t>PMS0024</t>
-  </si>
-  <si>
-    <t>Masterista Original Matcha 800Gr</t>
-  </si>
-  <si>
-    <t>PMS0026</t>
-  </si>
-  <si>
-    <t>Masterista Dark Chocolate 800Gr</t>
-  </si>
-  <si>
-    <t>PMS0122</t>
-  </si>
-  <si>
-    <t>Flavourista Syrup Lemon 1000 Ml</t>
-  </si>
-  <si>
-    <t>PMS0131</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Tropical Lychee 850 Ml</t>
-  </si>
-  <si>
-    <t>PMS0143</t>
-  </si>
-  <si>
-    <t>Masterista Syrup Premium Hazelnut 850 Ml</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160052</t>
-  </si>
-  <si>
-    <t>PVB0009</t>
-  </si>
-  <si>
-    <t>SLICER XS30 230V-50HZ-1PH RED (BKPXSGB50100000B0R)</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">East Bali  - Bangli </t>
-  </si>
-  <si>
-    <t>KOPI DANU KINTAMANI</t>
-  </si>
-  <si>
-    <t>PMS0036</t>
-  </si>
-  <si>
-    <t>Artisan Pure Matcha (500Gr/Pack)</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160054</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160055</t>
-  </si>
-  <si>
-    <t>ALILA HOTEL SEMINYAK</t>
-  </si>
-  <si>
-    <t>ASS-JT-LP250</t>
-  </si>
-  <si>
-    <t>Jasmine Tea @250gr/Pouch</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160057</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160059</t>
-  </si>
-  <si>
-    <t>ANVAYA HOTEL</t>
-  </si>
-  <si>
-    <t>PSW0004</t>
-  </si>
-  <si>
-    <t>Komi Teriyaki Sauce 1.9 L</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160061</t>
-  </si>
-  <si>
-    <t>FOOD GALLERIA</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160062</t>
-  </si>
-  <si>
-    <t>PSJ0032</t>
-  </si>
-  <si>
-    <t>Selecta Pork Belly Skin On</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160063</t>
-  </si>
-  <si>
-    <t>STHALA UBUD</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160064</t>
-  </si>
-  <si>
-    <t>RITZ CARLTON</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160065</t>
-  </si>
-  <si>
-    <t>FRANKIES BAR AND GRILL</t>
-  </si>
-  <si>
-    <t>PEA0005</t>
-  </si>
-  <si>
-    <t>Gold Box Melange Butter MP331 5 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160066</t>
-  </si>
-  <si>
-    <t>PMS0063</t>
-  </si>
-  <si>
-    <t>Flavorista Super Dark Chocolate 1kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160067</t>
-  </si>
-  <si>
-    <t>ROUMS COFE</t>
-  </si>
-  <si>
-    <t>POT0036</t>
-  </si>
-  <si>
-    <t>Premium Spicy Wedges 4x2.5 Kg</t>
-  </si>
-  <si>
-    <t>KTN</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160068</t>
-  </si>
-  <si>
-    <t>MAMAS GERMAN REST.</t>
-  </si>
-  <si>
-    <t>POS0025</t>
-  </si>
-  <si>
-    <t>O Sole Doppio Concentrato Paste Tomato 2.2 Kg</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160069</t>
-  </si>
-  <si>
-    <t>JACKSON LILY</t>
-  </si>
-  <si>
-    <t>SO-KU/2609/160070</t>
-  </si>
-  <si>
-    <t>ASKITCHEN JIMBARAN</t>
-  </si>
-  <si>
-    <t>Ni Ketut Sriasih (GT)</t>
+    <t>SO-KU/2610/160073</t>
   </si>
   <si>
     <t>KET</t>
@@ -1409,7 +1430,7 @@
     <tableColumn id="12" name="Qty BS" dataDxfId="1"/>
     <tableColumn id="13" name="KET"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1683,18 +1704,18 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11" style="8" customWidth="1"/>
-    <col min="8" max="8" width="42" style="8" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="22" style="8" customWidth="1"/>
+    <col min="6" max="6" width="15" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" style="8" customWidth="1"/>
     <col min="9" max="9" width="11" style="8" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="8" customWidth="1"/>
     <col min="12" max="12" width="8.85546875" style="10" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="11"/>
+    <col min="13" max="13" width="12.42578125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1735,335 +1756,335 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3">
-        <v>24</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L2" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J3" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J4" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L4" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46282</v>
+      <c r="A5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J5" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L5" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="3">
-        <v>5</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="3">
-        <v>5</v>
-      </c>
-      <c r="M6" t="s">
-        <v>248</v>
+        <v>51</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="15">
+        <v>12</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>248</v>
+        <v>55</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="15">
+        <v>48</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46282</v>
+      <c r="A8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J8" s="3">
-        <v>6</v>
+        <v>288</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="L8" s="3">
-        <v>6</v>
+        <v>288</v>
       </c>
       <c r="M8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J9" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -2071,2336 +2092,2336 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="3">
-        <v>12</v>
-      </c>
-      <c r="M10" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J11" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="L11" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M11" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L12" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M12" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J13" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="L13" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M13" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>40</v>
+      <c r="A16" s="12">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46312</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J16" s="3">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
+      <c r="A17" s="12">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46312</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2</v>
-      </c>
-      <c r="M17" t="s">
-        <v>248</v>
+        <v>80</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="15">
+        <v>1</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46282</v>
+      <c r="A18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J18" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="L18" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J19" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L19" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M19" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J20" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L20" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M20" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L21" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M21" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J22" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L22" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J23" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L23" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M23" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J24" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="L24" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M24" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J25" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L25" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J26" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="L26" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="3">
         <v>30</v>
       </c>
-      <c r="B27" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="L27" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M27" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="L28" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J29" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="L29" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+      <c r="A30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="15">
+        <v>3</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <v>23</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" s="3">
-        <v>180</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L30" s="3">
-        <v>180</v>
-      </c>
-      <c r="M30" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J31" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="L31" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M31" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
-        <v>36</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46282</v>
+      <c r="A32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J32" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L32" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M32" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M33" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B34" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="L34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="L35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M35" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B36" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>45</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46282</v>
+      <c r="A37" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
-        <v>46</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46282</v>
+      <c r="A38" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>189</v>
+        <v>94</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J38" s="3">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="L38" s="3">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="L39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>40</v>
+      <c r="A40" s="12">
+        <v>32</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46312</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="L40" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M40" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>40</v>
+      <c r="A41" s="12">
+        <v>34</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46312</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>40</v>
+        <v>174</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>194</v>
+        <v>26</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L41" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M41" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>40</v>
+      <c r="A42" s="12">
+        <v>36</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46312</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>19</v>
+        <v>184</v>
       </c>
       <c r="L42" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M42" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
-        <v>47</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46282</v>
+      <c r="A43" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>158</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="L43" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
-        <v>48</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46282</v>
+      <c r="A44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J44" s="3">
         <v>2</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="L44" s="3">
         <v>2</v>
       </c>
       <c r="M44" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="L45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="L46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B47" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="L47" s="3">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
-        <v>50</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46282</v>
+      <c r="A48" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J48" s="3">
         <v>2</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="L48" s="3">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B49" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
-        <v>52</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46282</v>
+      <c r="A50" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="L50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
-        <v>53</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46282</v>
+      <c r="A51" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J51" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="L51" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B52" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L52" s="3">
+        <v>3</v>
+      </c>
+      <c r="M52" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" s="3">
         <v>14</v>
       </c>
-      <c r="J52" s="3">
-        <v>4</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L52" s="3">
-        <v>4</v>
-      </c>
-      <c r="M52" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
-        <v>58</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="I53" s="1" t="s">
+      <c r="K53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L53" s="3">
         <v>14</v>
       </c>
-      <c r="J53" s="3">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L53" s="3">
-        <v>1</v>
-      </c>
       <c r="M53" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B54" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J54" s="3">
         <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>40</v>
+      <c r="A55" s="12">
+        <v>49</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46312</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L55" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B56" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>62</v>
+        <v>236</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L56" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
+        <v>51</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="G57" s="1" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J57" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L57" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
-        <v>9</v>
-      </c>
-      <c r="B58" s="2">
-        <v>46282</v>
+      <c r="A58" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="L58" s="3">
-        <v>100.04</v>
+        <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B59" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>64</v>
+        <v>241</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="3">
+        <v>12</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J59" s="3">
-        <v>5</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="L59" s="3">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="M59" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
+        <v>54</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="3">
         <v>12</v>
       </c>
-      <c r="B60" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J60" s="15">
-        <v>5</v>
-      </c>
-      <c r="K60" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="L60" s="15">
-        <v>0</v>
-      </c>
-      <c r="M60" s="16" t="s">
-        <v>249</v>
+      <c r="K60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60" s="3">
+        <v>12</v>
+      </c>
+      <c r="M60" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="B61" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>66</v>
+        <v>235</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>67</v>
+        <v>236</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J61" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="L61" s="3">
-        <v>18.28</v>
+        <v>2</v>
       </c>
       <c r="M61" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
+        <v>1</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B62" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H62" s="1" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="L62" s="3">
-        <v>6</v>
+        <v>202.43</v>
       </c>
       <c r="M62" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B63" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H63" s="1" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J63" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L63" s="3">
-        <v>7.29</v>
+        <v>20</v>
       </c>
       <c r="M63" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
+        <v>16</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J64" s="3">
-        <v>1</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="L64" s="3">
-        <v>1</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="M64" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B65" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J65" s="3">
         <v>1</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="L65" s="3">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B66" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="L66" s="3">
-        <v>1</v>
+        <v>65.23</v>
       </c>
       <c r="M66" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -4408,81 +4429,81 @@
         <v>25</v>
       </c>
       <c r="B67" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J67" s="3">
-        <v>2.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L67" s="3">
-        <v>2.1800000000000002</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M67" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>40</v>
+      <c r="A68" s="12">
+        <v>26</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46312</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L68" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M68" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -4490,614 +4511,614 @@
         <v>27</v>
       </c>
       <c r="B69" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L69" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M69" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B70" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L70" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M70" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B71" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J71" s="3">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L71" s="3">
-        <v>250</v>
+        <v>4931.4898999999996</v>
       </c>
       <c r="M71" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>40</v>
+      <c r="A72" s="12">
+        <v>35</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46312</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J72" s="3">
-        <v>75</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L72" s="3">
-        <v>75</v>
-      </c>
-      <c r="M72" t="s">
-        <v>248</v>
+        <v>178</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" s="15">
+        <v>14</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="15">
+        <v>0</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B73" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J73" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L73" s="3">
-        <v>100</v>
+        <v>10.4</v>
       </c>
       <c r="M73" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
+        <v>40</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" s="3">
+        <v>3</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L74" s="3">
+        <v>3</v>
+      </c>
+      <c r="M74" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="12">
+        <v>41</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46312</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B74" s="2">
-        <v>46282</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J74" s="3">
-        <v>40</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L74" s="3">
-        <v>40</v>
-      </c>
-      <c r="M74" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G75" s="1" t="s">
-        <v>168</v>
+        <v>30</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J75" s="3">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L75" s="3">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="M75" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B76" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>168</v>
+        <v>30</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J76" s="3">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L76" s="3">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M76" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B77" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>153</v>
+        <v>39</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J77" s="3">
-        <v>9.1998999999999995</v>
+        <v>1</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L77" s="3">
-        <v>8.77</v>
+        <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B78" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>132</v>
+        <v>220</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J78" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="L78" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B79" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J79" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L79" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M79" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B80" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>101</v>
+        <v>225</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J80" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="L80" s="3">
-        <v>27.6999</v>
+        <v>2</v>
       </c>
       <c r="M80" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B81" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>105</v>
+        <v>244</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="L81" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M81" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B82" s="2">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J82" s="3">
         <v>5</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="L82" s="3">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="M82" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B83" s="6">
-        <v>46282</v>
+        <v>46312</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="J83" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="L83" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M83" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
